--- a/Collections/Foreign_various/Foreighn_duplicates.xlsx
+++ b/Collections/Foreign_various/Foreighn_duplicates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Foreign_various\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76B19A9-2E61-4AD5-96B1-E9CFC3156A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B50622-5F62-42BB-87C9-DCC067B1052D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="112">
   <si>
     <t>-</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>Цена, ориентировочно</t>
+  </si>
+  <si>
+    <t>ГДР</t>
+  </si>
+  <si>
+    <t>1 пфенинг</t>
+  </si>
+  <si>
+    <t>Монетный двор A</t>
+  </si>
+  <si>
+    <t>ФРГ</t>
+  </si>
+  <si>
+    <t>10 пфенингов</t>
+  </si>
+  <si>
+    <t>Монетный двор J</t>
   </si>
 </sst>
 </file>
@@ -702,16 +720,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -721,6 +730,15 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9BE5FF"/>
@@ -963,6 +981,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFE5DFEC"/>
           <bgColor rgb="FFE5DFEC"/>
         </patternFill>
@@ -987,9 +1021,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Обзор всего-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="36"/>
-      <tableStyleElement type="firstRowStripe" dxfId="35"/>
-      <tableStyleElement type="secondRowStripe" dxfId="34"/>
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1011,9 +1045,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1282,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -2829,6 +2863,68 @@
         <v>12</v>
       </c>
     </row>
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="4">
+        <v>1952</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="8">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H54" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="I54" s="7">
+        <f>H54*$O$2</f>
+        <v>21.32</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4">
+        <v>1991</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="8">
+        <v>1</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H55" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="I55" s="7">
+        <f>H55*$O$2</f>
+        <v>10.66</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:E53" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="3">
@@ -2838,12 +2934,12 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F4:F7 F17">
-    <cfRule type="containsText" dxfId="33" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F7 F17">
-    <cfRule type="colorScale" priority="100">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2855,11 +2951,266 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="containsText" dxfId="32" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="containsText" dxfId="33" priority="95" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="containsText" dxfId="32" priority="93" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="colorScale" priority="94">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="containsText" dxfId="31" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="containsText" dxfId="30" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="containsText" dxfId="29" priority="83" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:F14">
+    <cfRule type="containsText" dxfId="28" priority="81" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:F14">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="containsText" dxfId="27" priority="79" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="containsText" dxfId="26" priority="77" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="containsText" dxfId="25" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="24" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="23" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="22" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="21" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="20" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="containsText" dxfId="19" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2871,13 +3222,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="containsText" dxfId="31" priority="91" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8">
-    <cfRule type="colorScale" priority="92">
+  <conditionalFormatting sqref="F27">
+    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F27">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2888,13 +3239,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="containsText" dxfId="30" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F9))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="colorScale" priority="90">
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2905,216 +3256,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="containsText" dxfId="29" priority="87" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="containsText" dxfId="28" priority="85" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="containsText" dxfId="27" priority="79" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F14">
-    <cfRule type="containsText" dxfId="26" priority="77" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13:F14">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="25" priority="75" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="24" priority="73" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="containsText" dxfId="23" priority="63" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F18">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="22" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="21" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="20" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="19" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="18" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="16" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3126,12 +3273,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
-    <cfRule type="containsText" dxfId="16" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27">
+  <conditionalFormatting sqref="F28">
+    <cfRule type="containsText" dxfId="15" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F31 F33:F42">
+    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29:F31 F33:F42">
     <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3143,13 +3307,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="F43">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F43))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3160,13 +3324,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="14" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="F44:F45">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F44))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44:F45">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3177,46 +3341,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F31 F33:F42">
-    <cfRule type="containsText" dxfId="12" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29:F31 F33:F42">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
+  <conditionalFormatting sqref="F46:F48">
     <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F46))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46:F48">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3228,12 +3358,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F44:F45">
+  <conditionalFormatting sqref="F49">
     <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F44))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F44:F45">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3245,12 +3375,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F46:F48">
+  <conditionalFormatting sqref="F50">
     <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F46))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F46:F48">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3262,12 +3392,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
+  <conditionalFormatting sqref="F51">
     <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F51">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3279,12 +3409,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
+  <conditionalFormatting sqref="F52">
     <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F52))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3296,13 +3426,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F51">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="F53">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F53))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3313,12 +3443,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52">
+  <conditionalFormatting sqref="F32">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F52))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F52">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3330,13 +3460,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F53))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
-    <cfRule type="colorScale" priority="101">
+  <conditionalFormatting sqref="F54">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3347,12 +3477,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
+  <conditionalFormatting sqref="F55">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3416,10 +3546,12 @@
     <hyperlink ref="J53" r:id="rId49" xr:uid="{246EE0BE-B71E-448D-BEDD-42B0125A584D}"/>
     <hyperlink ref="J30" r:id="rId50" xr:uid="{F92A4148-4754-431F-993D-E00DDB823E84}"/>
     <hyperlink ref="J32" r:id="rId51" xr:uid="{FBC9555C-B864-4E82-926A-09CDCE70881B}"/>
+    <hyperlink ref="J54" r:id="rId52" xr:uid="{CA474B78-2B45-4BF5-81DE-608ED7E2BC04}"/>
+    <hyperlink ref="J55" r:id="rId53" xr:uid="{0FC73EC6-88D0-481E-A8BB-8BD46C00EF5B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId52"/>
-  <legacyDrawing r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId54"/>
+  <legacyDrawing r:id="rId55"/>
 </worksheet>
 </file>
 
